--- a/gasman_api/examples/gasman_template.xlsx
+++ b/gasman_api/examples/gasman_template.xlsx
@@ -63,10 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -566,6 +567,7 @@
         <v>0.18</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -643,6 +645,7 @@
         <v>75</v>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
@@ -699,7 +702,7 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>00:00:00</t>
         </is>
@@ -726,7 +729,7 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>00:01:00</t>
         </is>
@@ -753,7 +756,7 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>00:05:00</t>
         </is>
@@ -780,7 +783,7 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>00:10:00</t>
         </is>
@@ -794,6 +797,156 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="24">
+      <c r="D24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="D25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="D27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="D29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="D32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="D33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="D35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="D36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="D37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="D38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="D39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="D40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="D41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="D42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="D43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="D54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="D55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="D61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="D64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="D65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="D70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="D71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="D72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="D73" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
